--- a/sample_data/Sample_Inward_Register.xlsx
+++ b/sample_data/Sample_Inward_Register.xlsx
@@ -14,11 +14,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="39">
   <si>
     <t>Supplier GSTIN</t>
   </si>
   <si>
+    <t>Supplier Name</t>
+  </si>
+  <si>
     <t>Invoice Number</t>
   </si>
   <si>
@@ -40,19 +43,34 @@
     <t>SGST Amount</t>
   </si>
   <si>
+    <t>Total Amount</t>
+  </si>
+  <si>
     <t>Cess Amount</t>
   </si>
   <si>
-    <t>Total Amount</t>
-  </si>
-  <si>
-    <t>29ABCDE1234F1Z5</t>
-  </si>
-  <si>
-    <t>27PQRSX5678L1Z2</t>
-  </si>
-  <si>
-    <t>07ZZZZZ9999A1Z1</t>
+    <t>29ABCDE1234F1ZW</t>
+  </si>
+  <si>
+    <t>27PQRSX5678L1ZW</t>
+  </si>
+  <si>
+    <t>07ZZZZZ9999A1ZP</t>
+  </si>
+  <si>
+    <t>29KLMNO4321Q1Z7</t>
+  </si>
+  <si>
+    <t>Sunrise Trading Company Pvt Ltd</t>
+  </si>
+  <si>
+    <t>Meridian Steels LLP</t>
+  </si>
+  <si>
+    <t>Meridian Steels</t>
+  </si>
+  <si>
+    <t>Orbit Chemicals Limited</t>
   </si>
   <si>
     <t>INV-1001</t>
@@ -70,44 +88,57 @@
     <t>INV-1005</t>
   </si>
   <si>
-    <t>INV-REG-ONLY</t>
-  </si>
-  <si>
-    <t>01-12-2025</t>
-  </si>
-  <si>
-    <t>05-12-2025</t>
-  </si>
-  <si>
-    <t>08-12-2025</t>
-  </si>
-  <si>
-    <t>10-12-2025</t>
-  </si>
-  <si>
-    <t>12-12-2025</t>
-  </si>
-  <si>
-    <t>15-12-2025</t>
-  </si>
-  <si>
-    <t>Dec-25</t>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>INV-1007</t>
+  </si>
+  <si>
+    <t>INV-1009</t>
+  </si>
+  <si>
+    <t>OC-2001</t>
+  </si>
+  <si>
+    <t>REG-ONLY-01</t>
+  </si>
+  <si>
+    <t>01-06-2026</t>
+  </si>
+  <si>
+    <t>05-06-2026</t>
+  </si>
+  <si>
+    <t>08-06-2026</t>
+  </si>
+  <si>
+    <t>12-06-2026</t>
+  </si>
+  <si>
+    <t>14-06-2026</t>
+  </si>
+  <si>
+    <t>16-06-2026</t>
+  </si>
+  <si>
+    <t>20-06-2026</t>
+  </si>
+  <si>
+    <t>22-06-2026</t>
+  </si>
+  <si>
+    <t>25-06-2026</t>
+  </si>
+  <si>
+    <t>Jun-26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -123,7 +154,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -131,30 +162,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,62 +462,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2">
         <v>10000</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>1800</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -515,28 +531,31 @@
       <c r="J2">
         <v>11800</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3">
         <v>20000</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>3590</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -547,42 +566,48 @@
       <c r="J3">
         <v>23590</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4">
         <v>15000</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>1350</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="J4">
         <v>17700</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
@@ -591,16 +616,16 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5">
         <v>5000</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>900</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -611,28 +636,28 @@
       <c r="J5">
         <v>5900</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6">
         <v>8000</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>1440</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -643,37 +668,218 @@
       <c r="J6">
         <v>9440</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
       </c>
       <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>12000</v>
+      </c>
+      <c r="G7">
+        <v>2160</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>14160</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="E7">
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8">
+        <v>10000</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>900</v>
+      </c>
+      <c r="I8">
+        <v>900</v>
+      </c>
+      <c r="J8">
+        <v>11800</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9">
+        <v>12000</v>
+      </c>
+      <c r="G9">
+        <v>2160</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>14160</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10">
+        <v>8000</v>
+      </c>
+      <c r="G10">
+        <v>1440</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>9440</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11">
+        <v>50000</v>
+      </c>
+      <c r="G11">
+        <v>9000</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>59000</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12">
         <v>3000</v>
       </c>
-      <c r="F7">
+      <c r="G12">
         <v>540</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
         <v>3540</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/Sample_Inward_Register.xlsx
+++ b/sample_data/Sample_Inward_Register.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="43">
   <si>
     <t>Supplier GSTIN</t>
   </si>
@@ -43,12 +43,12 @@
     <t>SGST Amount</t>
   </si>
   <si>
+    <t>Cess Amount</t>
+  </si>
+  <si>
     <t>Total Amount</t>
   </si>
   <si>
-    <t>Cess Amount</t>
-  </si>
-  <si>
     <t>29ABCDE1234F1ZW</t>
   </si>
   <si>
@@ -100,6 +100,12 @@
     <t>OC-2001</t>
   </si>
   <si>
+    <t>INV-1010</t>
+  </si>
+  <si>
+    <t>PURCH-77</t>
+  </si>
+  <si>
     <t>REG-ONLY-01</t>
   </si>
   <si>
@@ -125,6 +131,12 @@
   </si>
   <si>
     <t>22-06-2026</t>
+  </si>
+  <si>
+    <t>24-06-2026</t>
+  </si>
+  <si>
+    <t>26-06-2026</t>
   </si>
   <si>
     <t>25-06-2026</t>
@@ -462,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -511,10 +523,10 @@
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F2">
         <v>10000</v>
@@ -529,10 +541,10 @@
         <v>0</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>11800</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -546,10 +558,10 @@
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F3">
         <v>20000</v>
@@ -564,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>23590</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -581,10 +593,10 @@
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F4">
         <v>15000</v>
@@ -599,10 +611,10 @@
         <v>1350</v>
       </c>
       <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>17700</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -616,10 +628,10 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F5">
         <v>5000</v>
@@ -634,10 +646,10 @@
         <v>0</v>
       </c>
       <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>5900</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -648,10 +660,10 @@
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F6">
         <v>8000</v>
@@ -666,10 +678,10 @@
         <v>0</v>
       </c>
       <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>9440</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -683,10 +695,10 @@
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F7">
         <v>12000</v>
@@ -701,10 +713,10 @@
         <v>0</v>
       </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>14160</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -718,10 +730,10 @@
         <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F8">
         <v>10000</v>
@@ -736,10 +748,10 @@
         <v>900</v>
       </c>
       <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>11800</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -753,10 +765,10 @@
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F9">
         <v>12000</v>
@@ -771,10 +783,10 @@
         <v>0</v>
       </c>
       <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>14160</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -788,10 +800,10 @@
         <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F10">
         <v>8000</v>
@@ -806,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>9440</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -823,10 +835,10 @@
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F11">
         <v>50000</v>
@@ -841,45 +853,115 @@
         <v>0</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>59000</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
         <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F12">
+        <v>30000</v>
+      </c>
+      <c r="G12">
+        <v>5400</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>35400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13">
+        <v>6000</v>
+      </c>
+      <c r="G13">
+        <v>1080</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>7080</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14">
         <v>3000</v>
       </c>
-      <c r="G12">
+      <c r="G14">
         <v>540</v>
       </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <v>3540</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
